--- a/artfynd/S 486-2024 artfynd.xlsx
+++ b/artfynd/S 486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373587</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62331675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373564</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62331677</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118481639</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118481631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102046714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110427722</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111502568</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102046698</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558891</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119461061</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94693885</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128752</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2271,6 +2346,11 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050498</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,6 +2453,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88983363</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2475,6 +2560,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88983386</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2572,6 +2662,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88983387</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2669,6 +2764,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88983388</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2766,6 +2866,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88983389</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
           <t>PÖN0090 Alby-Tovåsen rovfågel, lom och skogshöns 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367321</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88983391</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3092,6 +3207,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82923562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3189,6 +3309,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571914</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3297,6 +3422,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106808620</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3399,6 +3529,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913228</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3496,6 +3631,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571860</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,6 +3738,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913229</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3700,6 +3845,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913231</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3797,6 +3947,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571852</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3894,6 +4049,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571855</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3991,6 +4151,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4093,6 +4258,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913230</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4195,6 +4365,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913227</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4301,6 +4476,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571878</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4407,6 +4587,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913311</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4513,6 +4698,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913313</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4615,6 +4805,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571877</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4712,6 +4907,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571853</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4809,6 +5009,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571859</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4911,6 +5116,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913243</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5013,6 +5223,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913234</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5124,6 +5339,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86913233</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5245,6 +5465,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926785</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5342,6 +5567,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959138</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5439,6 +5669,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955726</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5536,6 +5771,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571803</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5646,6 +5886,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571801</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5756,6 +6001,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571802</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5866,6 +6116,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571804</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5976,6 +6231,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571805</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6100,6 +6360,11 @@
           <t>PÖN0090 Alby-Tovåsen rovfågel, lom och skogshöns 2023</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113366835</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6224,6 +6489,11 @@
           <t>PÖN0090 Alby-Tovåsen rovfågel, lom och skogshöns 2023</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113366836</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6348,6 +6618,11 @@
           <t>PÖN0090 Alby-Tovåsen rovfågel, lom och skogshöns 2023</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113366839</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6472,6 +6747,11 @@
           <t>PÖN0090 Alby-Tovåsen rovfågel, lom och skogshöns 2023</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113366840</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6596,6 +6876,11 @@
           <t>PÖN0090 Alby-Tovåsen rovfågel, lom och skogshöns 2023</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113366841</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6697,6 +6982,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571800</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6794,6 +7084,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571799</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6891,6 +7186,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956695</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7017,6 +7317,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61737719</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7124,6 +7429,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54997066</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7226,6 +7536,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569370</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7328,6 +7643,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131008128</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7430,6 +7750,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131008129</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7532,6 +7857,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131008063</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7634,6 +7964,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569352</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7736,6 +8071,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569353</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7838,6 +8178,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569358</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7940,6 +8285,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569310</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8042,6 +8392,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569356</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8165,6 +8520,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108548562</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8284,8 +8644,87 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108548563</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 486-2024 artfynd.xlsx
+++ b/artfynd/S 486-2024 artfynd.xlsx
@@ -5476,7 +5476,7 @@
         <v>134959138</v>
       </c>
       <c r="B46" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>134955726</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>134956695</v>
       </c>
       <c r="B60" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
